--- a/data/trans_dic/P6905-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,51; 60,06</t>
+          <t>27,19; 59,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,74; 66,07</t>
+          <t>32,74; 65,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,74; 48,35</t>
+          <t>20,72; 47,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 64,29</t>
+          <t>20,43; 65,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,37; 80,76</t>
+          <t>45,42; 82,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,53; 84,16</t>
+          <t>48,96; 85,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,33; 65,74</t>
+          <t>33,38; 66,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,26; 66,42</t>
+          <t>29,01; 67,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,57; 63,36</t>
+          <t>39,12; 64,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,02; 68,89</t>
+          <t>44,35; 68,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,0; 50,55</t>
+          <t>29,58; 50,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,91; 59,32</t>
+          <t>28,74; 59,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 36,46</t>
+          <t>13,36; 38,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 41,93</t>
+          <t>18,09; 42,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,65; 43,35</t>
+          <t>22,99; 43,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 38,11</t>
+          <t>8,34; 41,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,0; 42,88</t>
+          <t>14,29; 42,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 39,59</t>
+          <t>8,64; 37,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,94; 57,84</t>
+          <t>29,1; 58,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,32; 68,54</t>
+          <t>41,78; 68,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,39; 34,6</t>
+          <t>16,49; 34,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 36,66</t>
+          <t>17,01; 35,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,9; 45,12</t>
+          <t>27,71; 44,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,39; 49,52</t>
+          <t>28,83; 50,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,67; 43,24</t>
+          <t>12,69; 42,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 51,07</t>
+          <t>11,87; 48,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 33,64</t>
+          <t>3,88; 30,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,04</t>
+          <t>0,0; 13,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 41,13</t>
+          <t>4,66; 41,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 46,99</t>
+          <t>5,95; 47,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,61</t>
+          <t>0,0; 42,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,57; 29,81</t>
+          <t>12,02; 30,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 37,66</t>
+          <t>13,01; 35,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 40,45</t>
+          <t>13,87; 40,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 26,84</t>
+          <t>5,18; 28,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 18,37</t>
+          <t>6,54; 17,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,94; 37,67</t>
+          <t>13,81; 37,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 31,8</t>
+          <t>8,16; 33,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 59,53</t>
+          <t>22,89; 59,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,37; 59,9</t>
+          <t>19,82; 60,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 54,75</t>
+          <t>14,97; 54,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,54; 69,34</t>
+          <t>30,57; 67,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,89; 71,22</t>
+          <t>36,14; 70,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 47,82</t>
+          <t>6,52; 46,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 38,44</t>
+          <t>18,86; 39,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,31; 41,57</t>
+          <t>20,1; 41,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,73; 60,23</t>
+          <t>34,56; 60,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 45,66</t>
+          <t>12,25; 44,66</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 44,87</t>
+          <t>10,49; 45,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,79</t>
+          <t>5,52; 44,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 70,93</t>
+          <t>19,3; 72,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 32,19</t>
+          <t>3,96; 33,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,11; 85,57</t>
+          <t>14,12; 85,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 91,1</t>
+          <t>30,38; 90,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,42; 100,0</t>
+          <t>19,22; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 36,32</t>
+          <t>3,48; 35,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,23; 49,37</t>
+          <t>15,95; 50,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,89; 60,62</t>
+          <t>21,98; 59,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,53; 73,14</t>
+          <t>27,92; 73,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 27,09</t>
+          <t>6,53; 28,29</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,2; 61,89</t>
+          <t>31,53; 63,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,95; 39,03</t>
+          <t>11,71; 39,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 32,4</t>
+          <t>4,17; 31,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,33; 36,48</t>
+          <t>9,2; 36,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,89; 86,24</t>
+          <t>38,49; 87,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 50,61</t>
+          <t>6,27; 50,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,96; 87,19</t>
+          <t>13,65; 87,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 38,18</t>
+          <t>14,71; 38,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,42; 65,7</t>
+          <t>38,3; 63,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,26; 35,69</t>
+          <t>13,49; 35,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 39,33</t>
+          <t>9,86; 41,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,14; 33,56</t>
+          <t>14,62; 32,18</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,3; 45,65</t>
+          <t>22,63; 43,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,08; 42,92</t>
+          <t>16,89; 42,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 26,86</t>
+          <t>8,82; 27,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,71; 37,08</t>
+          <t>15,55; 35,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,52; 54,22</t>
+          <t>26,26; 55,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,9; 58,61</t>
+          <t>26,66; 57,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,19; 51,48</t>
+          <t>24,54; 52,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,9; 50,52</t>
+          <t>29,69; 50,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,37; 43,61</t>
+          <t>27,42; 44,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,72; 44,07</t>
+          <t>25,79; 45,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,93; 33,13</t>
+          <t>18,46; 33,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,42; 39,62</t>
+          <t>25,78; 40,27</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,15; 35,53</t>
+          <t>18,64; 34,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 26,0</t>
+          <t>4,61; 26,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,49; 42,54</t>
+          <t>13,06; 41,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,98; 37,96</t>
+          <t>14,66; 38,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,39; 57,69</t>
+          <t>30,37; 58,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,93; 58,44</t>
+          <t>17,88; 58,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 39,56</t>
+          <t>4,55; 39,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,41; 50,34</t>
+          <t>15,5; 51,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,51; 39,42</t>
+          <t>24,54; 39,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 33,65</t>
+          <t>12,27; 34,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 35,71</t>
+          <t>13,18; 36,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,83; 39,16</t>
+          <t>18,04; 38,68</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,47; 34,65</t>
+          <t>26,21; 35,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,41; 31,37</t>
+          <t>21,42; 30,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,91; 32,71</t>
+          <t>22,48; 32,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,89; 29,25</t>
+          <t>18,32; 28,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,05; 47,36</t>
+          <t>34,53; 47,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,47; 48,33</t>
+          <t>33,72; 48,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,99; 48,37</t>
+          <t>34,46; 48,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,67; 38,34</t>
+          <t>23,43; 38,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,19; 37,43</t>
+          <t>29,6; 37,08</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27,81; 36,27</t>
+          <t>28,28; 35,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28,26; 36,42</t>
+          <t>28,62; 36,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,13; 31,49</t>
+          <t>23,19; 31,74</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11788; 25732</t>
+          <t>11650; 25620</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12931; 26092</t>
+          <t>12928; 25887</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12149; 28321</t>
+          <t>12136; 27969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4370; 15474</t>
+          <t>4916; 15721</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12412; 23113</t>
+          <t>12998; 23473</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13857; 24534</t>
+          <t>14272; 24969</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14036; 26878</t>
+          <t>13645; 27267</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4453; 10465</t>
+          <t>4570; 10691</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27563; 45277</t>
+          <t>27954; 45805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30901; 47292</t>
+          <t>30447; 47228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29842; 50277</t>
+          <t>29421; 50366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11514; 23622</t>
+          <t>11445; 23801</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9865; 26399</t>
+          <t>9670; 27799</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10138; 23729</t>
+          <t>10235; 23900</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18750; 35884</t>
+          <t>19033; 36168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3216; 17639</t>
+          <t>3858; 19176</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4577; 14018</t>
+          <t>4672; 13843</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3097; 13587</t>
+          <t>2966; 12987</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11930; 24697</t>
+          <t>12424; 25063</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19685; 31146</t>
+          <t>18988; 31085</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17220; 36360</t>
+          <t>17333; 36629</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15727; 33322</t>
+          <t>15460; 32651</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35004; 56616</t>
+          <t>34769; 55895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26038; 45424</t>
+          <t>26447; 45923</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4273; 15833</t>
+          <t>4646; 15599</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2947; 12398</t>
+          <t>2881; 11760</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>843; 7150</t>
+          <t>824; 6392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5958</t>
+          <t>0; 6694</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1007; 8935</t>
+          <t>1012; 8911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>979; 8428</t>
+          <t>1066; 8512</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5326</t>
+          <t>0; 5333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4856; 13691</t>
+          <t>5522; 13969</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7756; 21972</t>
+          <t>7592; 20667</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5764; 17075</t>
+          <t>5854; 16950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1746; 9059</t>
+          <t>1748; 9462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6327; 17533</t>
+          <t>6243; 16729</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8716; 21971</t>
+          <t>8055; 22115</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3634; 14265</t>
+          <t>3661; 14953</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7615; 19326</t>
+          <t>7432; 19343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7815; 24170</t>
+          <t>7997; 24252</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3307; 12433</t>
+          <t>3399; 12407</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9315; 20480</t>
+          <t>9028; 19920</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10145; 21319</t>
+          <t>10819; 21136</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6629; 38566</t>
+          <t>5261; 37261</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14503; 31147</t>
+          <t>15280; 31696</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15108; 30927</t>
+          <t>14956; 30630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21047; 37581</t>
+          <t>21564; 37640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15303; 55248</t>
+          <t>14819; 54041</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1882; 10299</t>
+          <t>2409; 10448</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7242</t>
+          <t>893; 7149</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2338; 10548</t>
+          <t>2869; 10719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>677; 5716</t>
+          <t>703; 5887</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>983; 5964</t>
+          <t>984; 5964</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3411; 10624</t>
+          <t>3542; 10599</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1121; 5771</t>
+          <t>1109; 5771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>404; 3990</t>
+          <t>383; 3845</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4857; 14773</t>
+          <t>4774; 15093</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6092; 16869</t>
+          <t>6116; 16466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5682; 15097</t>
+          <t>5762; 15168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1779; 7786</t>
+          <t>1878; 8132</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12210; 25876</t>
+          <t>13185; 26749</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4751; 16930</t>
+          <t>5078; 17014</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>945; 7269</t>
+          <t>935; 7155</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2950; 11533</t>
+          <t>2908; 11490</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5058; 12154</t>
+          <t>5424; 12333</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>920; 7685</t>
+          <t>952; 7632</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1036; 6476</t>
+          <t>1014; 6481</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4234; 11535</t>
+          <t>4443; 11702</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20360; 36730</t>
+          <t>21411; 35734</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7763; 20900</t>
+          <t>7900; 20973</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2400; 11743</t>
+          <t>2943; 12400</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8745; 20751</t>
+          <t>9038; 19897</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20610; 40378</t>
+          <t>20014; 38098</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8752; 23361</t>
+          <t>9191; 23012</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7518; 21044</t>
+          <t>6913; 21418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11495; 27136</t>
+          <t>11381; 26106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11109; 23603</t>
+          <t>11431; 24256</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13869; 27185</t>
+          <t>12364; 26802</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14028; 28664</t>
+          <t>13663; 29175</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21087; 35629</t>
+          <t>20936; 35590</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36121; 57559</t>
+          <t>36191; 58428</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25930; 44429</t>
+          <t>26000; 45731</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24029; 44407</t>
+          <t>24745; 44766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>36524; 56939</t>
+          <t>37049; 57874</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20859; 38697</t>
+          <t>20306; 38070</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2884; 11998</t>
+          <t>2128; 12021</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5299; 16707</t>
+          <t>5130; 16426</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7935; 21547</t>
+          <t>8322; 21962</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15131; 28723</t>
+          <t>15120; 29290</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5498; 17924</t>
+          <t>5483; 17963</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>971; 8466</t>
+          <t>974; 8487</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8433; 27541</t>
+          <t>8479; 28199</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38895; 62558</t>
+          <t>38941; 62258</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9962; 25847</t>
+          <t>9426; 26648</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8121; 21665</t>
+          <t>7998; 22272</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19879; 43654</t>
+          <t>20114; 43110</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>120280; 163652</t>
+          <t>123771; 166150</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69651; 102071</t>
+          <t>69688; 100601</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>80193; 114490</t>
+          <t>78681; 112585</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60738; 99292</t>
+          <t>62196; 97889</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>77154; 104241</t>
+          <t>76002; 104901</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74043; 103828</t>
+          <t>72440; 103677</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75682; 104613</t>
+          <t>74529; 104549</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>83849; 135810</t>
+          <t>82978; 136476</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>209046; 259159</t>
+          <t>204964; 256786</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150211; 195919</t>
+          <t>152744; 193169</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160012; 206249</t>
+          <t>162076; 208156</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>160456; 218460</t>
+          <t>160841; 220170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6905-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,19; 59,8</t>
+          <t>27,02; 59,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,74; 65,55</t>
+          <t>33,38; 64,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,72; 47,75</t>
+          <t>20,88; 46,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,43; 65,31</t>
+          <t>15,1; 51,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,42; 82,02</t>
+          <t>40,77; 80,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,96; 85,65</t>
+          <t>48,6; 83,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,38; 66,69</t>
+          <t>35,6; 65,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,01; 67,86</t>
+          <t>25,91; 61,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,12; 64,1</t>
+          <t>39,11; 64,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,35; 68,8</t>
+          <t>44,3; 69,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,58; 50,64</t>
+          <t>30,25; 50,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,74; 59,77</t>
+          <t>23,38; 49,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,36; 38,4</t>
+          <t>14,16; 38,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,09; 42,23</t>
+          <t>17,94; 42,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,99; 43,69</t>
+          <t>22,8; 42,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 41,43</t>
+          <t>11,41; 43,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 42,35</t>
+          <t>14,07; 42,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 37,85</t>
+          <t>8,66; 37,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,1; 58,7</t>
+          <t>28,83; 59,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,78; 68,4</t>
+          <t>42,44; 67,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 34,86</t>
+          <t>16,08; 35,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,01; 35,92</t>
+          <t>17,86; 37,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,71; 44,54</t>
+          <t>28,16; 45,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,83; 50,07</t>
+          <t>28,51; 50,05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 42,6</t>
+          <t>12,83; 43,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 48,44</t>
+          <t>12,01; 48,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 30,07</t>
+          <t>3,87; 30,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,52</t>
+          <t>0,0; 11,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 41,02</t>
+          <t>4,63; 40,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 47,46</t>
+          <t>5,5; 46,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,66</t>
+          <t>0,0; 42,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,02; 30,42</t>
+          <t>10,63; 29,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,01; 35,43</t>
+          <t>12,12; 35,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 40,15</t>
+          <t>13,4; 39,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 28,03</t>
+          <t>5,0; 27,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 17,53</t>
+          <t>6,89; 17,93</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,81; 37,92</t>
+          <t>13,99; 38,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 33,33</t>
+          <t>7,08; 31,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,89; 59,58</t>
+          <t>23,18; 59,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 60,1</t>
+          <t>30,15; 68,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 54,64</t>
+          <t>14,42; 53,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 67,44</t>
+          <t>30,26; 69,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,14; 70,61</t>
+          <t>35,72; 73,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 46,2</t>
+          <t>30,04; 55,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 39,12</t>
+          <t>17,59; 38,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 41,17</t>
+          <t>19,87; 42,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,56; 60,32</t>
+          <t>34,42; 59,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,25; 44,66</t>
+          <t>34,98; 57,66</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 45,52</t>
+          <t>7,92; 44,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 44,21</t>
+          <t>5,6; 43,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,3; 72,09</t>
+          <t>16,83; 71,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 33,16</t>
+          <t>3,35; 28,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,12; 85,57</t>
+          <t>14,08; 85,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,38; 90,89</t>
+          <t>25,97; 90,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,22; 100,0</t>
+          <t>19,82; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 35,0</t>
+          <t>2,89; 29,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,95; 50,43</t>
+          <t>16,16; 50,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 59,17</t>
+          <t>18,48; 58,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,92; 73,48</t>
+          <t>28,44; 72,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 28,29</t>
+          <t>5,74; 23,98</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,53; 63,98</t>
+          <t>31,92; 62,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 39,22</t>
+          <t>11,43; 37,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 31,89</t>
+          <t>4,26; 35,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 36,34</t>
+          <t>8,79; 33,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,49; 87,5</t>
+          <t>36,13; 86,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 50,26</t>
+          <t>6,17; 50,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,65; 87,26</t>
+          <t>13,95; 87,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,71; 38,73</t>
+          <t>14,61; 38,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,3; 63,92</t>
+          <t>37,91; 64,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,49; 35,81</t>
+          <t>13,19; 37,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,86; 41,53</t>
+          <t>9,72; 40,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,62; 32,18</t>
+          <t>13,31; 31,26</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,63; 43,07</t>
+          <t>22,92; 43,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,89; 42,28</t>
+          <t>16,31; 41,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,82; 27,34</t>
+          <t>8,36; 26,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,55; 35,68</t>
+          <t>16,97; 39,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,26; 55,72</t>
+          <t>26,39; 56,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,66; 57,79</t>
+          <t>29,89; 60,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,54; 52,4</t>
+          <t>26,38; 52,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,69; 50,46</t>
+          <t>29,92; 49,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,42; 44,27</t>
+          <t>27,56; 43,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,79; 45,36</t>
+          <t>26,07; 45,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,46; 33,4</t>
+          <t>17,97; 33,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,78; 40,27</t>
+          <t>25,7; 40,81</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,64; 34,95</t>
+          <t>18,89; 35,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 26,05</t>
+          <t>6,25; 26,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,06; 41,83</t>
+          <t>14,36; 41,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,66; 38,69</t>
+          <t>15,45; 38,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,37; 58,83</t>
+          <t>30,21; 57,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,88; 58,57</t>
+          <t>17,47; 56,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 39,66</t>
+          <t>4,78; 42,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,5; 51,54</t>
+          <t>12,03; 32,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,54; 39,23</t>
+          <t>24,23; 39,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,27; 34,69</t>
+          <t>13,65; 34,24</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,18; 36,71</t>
+          <t>13,95; 37,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,04; 38,68</t>
+          <t>15,98; 31,63</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26,21; 35,18</t>
+          <t>25,66; 34,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,42; 30,92</t>
+          <t>21,08; 31,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,48; 32,17</t>
+          <t>22,77; 32,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,32; 28,83</t>
+          <t>20,28; 30,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,53; 47,66</t>
+          <t>34,12; 48,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,72; 48,26</t>
+          <t>33,92; 47,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,46; 48,34</t>
+          <t>34,96; 48,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,43; 38,53</t>
+          <t>28,95; 38,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,6; 37,08</t>
+          <t>29,8; 37,02</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28,28; 35,76</t>
+          <t>28,2; 36,87</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28,62; 36,76</t>
+          <t>28,67; 36,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,19; 31,74</t>
+          <t>26,02; 32,97</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>15012</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11650; 25620</t>
+          <t>11576; 25515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12928; 25887</t>
+          <t>13184; 25462</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12136; 27969</t>
+          <t>12232; 27467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4916; 15721</t>
+          <t>3959; 13492</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12998; 23473</t>
+          <t>11667; 23061</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14272; 24969</t>
+          <t>14169; 24387</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13645; 27267</t>
+          <t>14557; 26976</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4570; 10691</t>
+          <t>4199; 9898</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27954; 45805</t>
+          <t>27950; 45768</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30447; 47228</t>
+          <t>30407; 47521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29421; 50366</t>
+          <t>30086; 49868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11445; 23801</t>
+          <t>9918; 20813</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>25190</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>36414</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9670; 27799</t>
+          <t>10250; 27816</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10235; 23900</t>
+          <t>10155; 24115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19033; 36168</t>
+          <t>18875; 35356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3858; 19176</t>
+          <t>5479; 21000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4672; 13843</t>
+          <t>4600; 13789</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2966; 12987</t>
+          <t>2971; 12743</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12424; 25063</t>
+          <t>12310; 25358</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18988; 31085</t>
+          <t>19736; 31248</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17333; 36629</t>
+          <t>16892; 37164</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15460; 32651</t>
+          <t>16240; 34295</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34769; 55895</t>
+          <t>35337; 57070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26447; 45923</t>
+          <t>26945; 47299</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10924</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4646; 15599</t>
+          <t>4699; 16073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2881; 11760</t>
+          <t>2917; 11680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>824; 6392</t>
+          <t>822; 6385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6694</t>
+          <t>0; 5754</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1012; 8911</t>
+          <t>1006; 8781</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1066; 8512</t>
+          <t>987; 8318</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5333</t>
+          <t>0; 5252</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5522; 13969</t>
+          <t>4992; 13914</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7592; 20667</t>
+          <t>7072; 20691</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5854; 16950</t>
+          <t>5656; 16593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1748; 9462</t>
+          <t>1687; 9194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6243; 16729</t>
+          <t>6649; 17312</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35960</t>
+          <t>49613</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8055; 22115</t>
+          <t>8161; 22178</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3661; 14953</t>
+          <t>3174; 14277</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7432; 19343</t>
+          <t>7525; 19203</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7997; 24252</t>
+          <t>16334; 36949</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3399; 12407</t>
+          <t>3274; 12222</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9028; 19920</t>
+          <t>8939; 20547</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10819; 21136</t>
+          <t>10694; 21908</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5261; 37261</t>
+          <t>16008; 29733</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15280; 31696</t>
+          <t>14253; 31332</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14956; 30630</t>
+          <t>14781; 31701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21564; 37640</t>
+          <t>21477; 37392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14819; 54041</t>
+          <t>37582; 61958</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4390</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2409; 10448</t>
+          <t>1817; 10176</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>893; 7149</t>
+          <t>906; 7001</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2869; 10719</t>
+          <t>2502; 10696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703; 5887</t>
+          <t>725; 6129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>984; 5964</t>
+          <t>981; 5965</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3542; 10599</t>
+          <t>3029; 10589</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1109; 5771</t>
+          <t>1144; 5771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>383; 3845</t>
+          <t>392; 4033</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4774; 15093</t>
+          <t>4835; 15010</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6116; 16466</t>
+          <t>5144; 16319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5762; 15168</t>
+          <t>5870; 14956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1878; 8132</t>
+          <t>2022; 8451</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>13662</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13185; 26749</t>
+          <t>13347; 26138</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5078; 17014</t>
+          <t>4957; 16235</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>935; 7155</t>
+          <t>955; 7881</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2908; 11490</t>
+          <t>2890; 11129</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5424; 12333</t>
+          <t>5092; 12201</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>952; 7632</t>
+          <t>937; 7612</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1014; 6481</t>
+          <t>1036; 6518</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4443; 11702</t>
+          <t>4468; 11719</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21411; 35734</t>
+          <t>21194; 36230</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7900; 20973</t>
+          <t>7723; 21732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2943; 12400</t>
+          <t>2903; 12199</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9038; 19897</t>
+          <t>8443; 19836</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>54331</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20014; 38098</t>
+          <t>20276; 38873</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9191; 23012</t>
+          <t>8880; 22668</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6913; 21418</t>
+          <t>6552; 20684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11381; 26106</t>
+          <t>14573; 33503</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11431; 24256</t>
+          <t>11491; 24426</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12364; 26802</t>
+          <t>13862; 27883</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13663; 29175</t>
+          <t>14690; 29168</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20936; 35590</t>
+          <t>24147; 39882</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36191; 58428</t>
+          <t>36371; 57634</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26000; 45731</t>
+          <t>26279; 46090</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24745; 44766</t>
+          <t>24081; 45075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>37049; 57874</t>
+          <t>42805; 67980</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28936</t>
+          <t>28751</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20306; 38070</t>
+          <t>20575; 39109</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2128; 12021</t>
+          <t>2883; 12038</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5130; 16426</t>
+          <t>5638; 16186</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8322; 21962</t>
+          <t>10298; 25538</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15120; 29290</t>
+          <t>15040; 28730</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5483; 17963</t>
+          <t>5359; 17358</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>974; 8487</t>
+          <t>1022; 9079</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8479; 28199</t>
+          <t>6917; 18663</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38941; 62258</t>
+          <t>38447; 61939</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9426; 26648</t>
+          <t>10487; 26304</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7998; 22272</t>
+          <t>8465; 22584</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>20114; 43110</t>
+          <t>19838; 39259</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77549</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>115965</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>191958</t>
+          <t>213098</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>123771; 166150</t>
+          <t>121184; 162733</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69688; 100601</t>
+          <t>68592; 101076</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78681; 112585</t>
+          <t>79689; 114016</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62196; 97889</t>
+          <t>78078; 117943</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>76002; 104901</t>
+          <t>75100; 105759</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>72440; 103677</t>
+          <t>72880; 103075</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74529; 104549</t>
+          <t>75610; 105648</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>82978; 136476</t>
+          <t>99979; 134155</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>204964; 256786</t>
+          <t>206311; 256365</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152744; 193169</t>
+          <t>152324; 199139</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>162076; 208156</t>
+          <t>162334; 206760</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>160841; 220170</t>
+          <t>190026; 240821</t>
         </is>
       </c>
     </row>
